--- a/game31/web.xlsx
+++ b/game31/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="12960" windowHeight="4560"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
   <si>
     <t>domain</t>
   </si>
@@ -46,82 +46,64 @@
     <t>json</t>
   </si>
   <si>
-    <t>epigonium.com</t>
-  </si>
-  <si>
-    <t>#ffd9a3</t>
-  </si>
-  <si>
-    <t>#a37070</t>
-  </si>
-  <si>
-    <t>blennorrhea.com</t>
-  </si>
-  <si>
-    <t>#f597ba</t>
+    <t>play.circumundulate.com</t>
+  </si>
+  <si>
+    <t>#6b496a</t>
+  </si>
+  <si>
+    <t>#36435a</t>
+  </si>
+  <si>
+    <t>sec.circumundulate.com</t>
+  </si>
+  <si>
+    <t>game.circumundulate.com</t>
+  </si>
+  <si>
+    <t>rounces.top</t>
+  </si>
+  <si>
+    <t>#ffa500</t>
+  </si>
+  <si>
+    <t>#bce3fe</t>
+  </si>
+  <si>
+    <t>banderole.top</t>
+  </si>
+  <si>
+    <t>#def0f9</t>
   </si>
   <si>
     <t>#4167b1</t>
   </si>
   <si>
-    <t>cataclinal.com</t>
-  </si>
-  <si>
-    <t>#b8f500</t>
+    <t>peytrels.top</t>
+  </si>
+  <si>
+    <t>#f8e9a1</t>
   </si>
   <si>
     <t>#d62828</t>
   </si>
   <si>
-    <t>jaculation.com</t>
-  </si>
-  <si>
-    <t>#bdd0c4</t>
+    <t>lintels.fun</t>
+  </si>
+  <si>
+    <t>#f9f0ed</t>
   </si>
   <si>
     <t>#e58889</t>
   </si>
   <si>
-    <t>labialism.com</t>
-  </si>
-  <si>
-    <t>#f0ff31</t>
+    <t>nargilehs.fun</t>
+  </si>
+  <si>
+    <t>#ebdec6</t>
   </si>
   <si>
     <t>#b57743</t>
-  </si>
-  <si>
-    <t>rounces.top</t>
-  </si>
-  <si>
-    <t>#ffa500</t>
-  </si>
-  <si>
-    <t>#bce3fe</t>
-  </si>
-  <si>
-    <t>banderole.top</t>
-  </si>
-  <si>
-    <t>#def0f9</t>
-  </si>
-  <si>
-    <t>peytrels.top</t>
-  </si>
-  <si>
-    <t>#f8e9a1</t>
-  </si>
-  <si>
-    <t>lintels.fun</t>
-  </si>
-  <si>
-    <t>#f9f0ed</t>
-  </si>
-  <si>
-    <t>nargilehs.fun</t>
-  </si>
-  <si>
-    <t>#ebdec6</t>
   </si>
   <si>
     <t>color</t>
@@ -176,7 +158,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -239,6 +221,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF175CEB"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -397,7 +394,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="54">
+  <fills count="52">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -496,25 +493,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD9A3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA37070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF597BA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8F500"/>
+        <fgColor rgb="FF6B496A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36435A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -826,28 +811,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -856,122 +832,131 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1033,35 +1018,20 @@
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1448,6 +1418,9 @@
   <sheetPr/>
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="19.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1466,98 +1439,72 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="23" t="s">
         <v>7</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>10</v>
+      <c r="C3" s="23" t="s">
+        <v>7</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>13</v>
+      <c r="C4" s="23" t="s">
+        <v>7</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="epigonium.com"/>
-    <hyperlink ref="A3" r:id="rId2" display="blennorrhea.com"/>
-    <hyperlink ref="A4" r:id="rId3" display="cataclinal.com"/>
-    <hyperlink ref="A5" r:id="rId4" display="jaculation.com"/>
-    <hyperlink ref="A6" r:id="rId5" display="labialism.com"/>
+    <hyperlink ref="A2" r:id="rId1" display="play.circumundulate.com" tooltip="http://play.circumundulate.com"/>
+    <hyperlink ref="A3" r:id="rId2" display="sec.circumundulate.com" tooltip="http://sec.circumundulate.com"/>
+    <hyperlink ref="A4" r:id="rId3" display="game.circumundulate.com" tooltip="http://game.circumundulate.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1586,62 +1533,62 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="10" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" s="10"/>
     </row>
     <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="10" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
     <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="10" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="10" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -1673,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1687,10 +1634,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1701,10 +1648,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1715,10 +1662,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1729,10 +1676,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1743,10 +1690,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1757,18 +1704,18 @@
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
